--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="17">
   <si>
     <t>H001</t>
   </si>
@@ -36,9 +36,6 @@
     <t>Luxury Rose Gold Pull</t>
   </si>
   <si>
-    <t>Limited</t>
-  </si>
-  <si>
     <t>M010</t>
   </si>
   <si>
@@ -49,9 +46,6 @@
   </si>
   <si>
     <t>Pooja Mandir Knob</t>
-  </si>
-  <si>
-    <t>Out of Stock</t>
   </si>
   <si>
     <t>G009</t>
@@ -452,22 +446,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -507,15 +501,15 @@
         <v>3</v>
       </c>
       <c r="F3" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
         <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
       </c>
       <c r="C4">
         <v>6000</v>
@@ -524,7 +518,7 @@
         <v>5500</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
         <v>2</v>
@@ -532,10 +526,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
         <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
       </c>
       <c r="C5">
         <v>500</v>
@@ -544,18 +538,18 @@
         <v>450</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C6">
         <v>4000</v>
@@ -564,7 +558,7 @@
         <v>3200</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
         <v>2</v>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -33,9 +33,6 @@
     <t>H002</t>
   </si>
   <si>
-    <t>Luxury Rose Gold Pull</t>
-  </si>
-  <si>
     <t>M010</t>
   </si>
   <si>
@@ -45,9 +42,6 @@
     <t>P005</t>
   </si>
   <si>
-    <t>Pooja Mandir Knob</t>
-  </si>
-  <si>
     <t>G009</t>
   </si>
   <si>
@@ -70,6 +64,12 @@
   </si>
   <si>
     <t>status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SHINE DOOR HANDLE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JAYA DOOR HANDLE </t>
   </si>
 </sst>
 </file>
@@ -446,22 +446,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -489,10 +489,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C3">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="D3">
         <v>2800</v>
@@ -506,10 +506,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
         <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
       </c>
       <c r="C4">
         <v>6000</v>
@@ -518,7 +518,7 @@
         <v>5500</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4" t="s">
         <v>2</v>
@@ -526,19 +526,19 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C5">
-        <v>500</v>
+        <v>3000</v>
       </c>
       <c r="D5">
         <v>450</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
         <v>2</v>
@@ -546,10 +546,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C6">
         <v>4000</v>
@@ -558,7 +558,7 @@
         <v>3200</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
         <v>2</v>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -36,9 +36,6 @@
     <t>M010</t>
   </si>
   <si>
-    <t>MOP Inlay Handle</t>
-  </si>
-  <si>
     <t>P005</t>
   </si>
   <si>
@@ -70,6 +67,9 @@
   </si>
   <si>
     <t xml:space="preserve">JAYA DOOR HANDLE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PUSHPA DOOR HANDLE </t>
   </si>
 </sst>
 </file>
@@ -446,22 +446,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -489,7 +489,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3">
         <v>8000</v>
@@ -509,7 +509,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C4">
         <v>6000</v>
@@ -526,10 +526,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C5">
         <v>3000</v>
@@ -538,7 +538,7 @@
         <v>450</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F5" t="s">
         <v>2</v>
@@ -546,10 +546,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
         <v>7</v>
-      </c>
-      <c r="B6" t="s">
-        <v>8</v>
       </c>
       <c r="C6">
         <v>4000</v>
@@ -558,7 +558,7 @@
         <v>3200</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
         <v>2</v>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
   <si>
     <t>H001</t>
   </si>
@@ -70,6 +70,21 @@
   </si>
   <si>
     <t xml:space="preserve">PUSHPA DOOR HANDLE </t>
+  </si>
+  <si>
+    <t>H001.PNG</t>
+  </si>
+  <si>
+    <t>H002.PNG</t>
+  </si>
+  <si>
+    <t>M010.PNG</t>
+  </si>
+  <si>
+    <t>P005.PNG</t>
+  </si>
+  <si>
+    <t>G009.PNG</t>
   </si>
 </sst>
 </file>
@@ -478,7 +493,7 @@
         <v>50000</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F2" t="s">
         <v>2</v>
@@ -498,7 +513,7 @@
         <v>2800</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="F3" t="s">
         <v>2</v>
@@ -518,7 +533,7 @@
         <v>5500</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F4" t="s">
         <v>2</v>
@@ -538,7 +553,7 @@
         <v>450</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F5" t="s">
         <v>2</v>
@@ -558,7 +573,7 @@
         <v>3200</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F6" t="s">
         <v>2</v>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -72,19 +72,19 @@
     <t xml:space="preserve">PUSHPA DOOR HANDLE </t>
   </si>
   <si>
-    <t>H001.PNG</t>
-  </si>
-  <si>
-    <t>H002.PNG</t>
-  </si>
-  <si>
-    <t>M010.PNG</t>
-  </si>
-  <si>
-    <t>P005.PNG</t>
-  </si>
-  <si>
-    <t>G009.PNG</t>
+    <t>H001.JPG</t>
+  </si>
+  <si>
+    <t>H002.JPG</t>
+  </si>
+  <si>
+    <t>M010.JPG</t>
+  </si>
+  <si>
+    <t>P005.JPG</t>
+  </si>
+  <si>
+    <t>G009.JPG</t>
   </si>
 </sst>
 </file>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -1,119 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BeSecureAdmin\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8556"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
-  <si>
-    <t>H001</t>
-  </si>
-  <si>
-    <t>LOTUS DOOR HANDLE</t>
-  </si>
-  <si>
-    <t>Available</t>
-  </si>
-  <si>
-    <t>H002</t>
-  </si>
-  <si>
-    <t>M010</t>
-  </si>
-  <si>
-    <t>P005</t>
-  </si>
-  <si>
-    <t>G009</t>
-  </si>
-  <si>
-    <t>Crystal Glass Handle</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>mrp</t>
-  </si>
-  <si>
-    <t>rate</t>
-  </si>
-  <si>
-    <t>image_name</t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SHINE DOOR HANDLE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">JAYA DOOR HANDLE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">PUSHPA DOOR HANDLE </t>
-  </si>
-  <si>
-    <t>H001.JPG</t>
-  </si>
-  <si>
-    <t>H002.JPG</t>
-  </si>
-  <si>
-    <t>M010.JPG</t>
-  </si>
-  <si>
-    <t>P005.JPG</t>
-  </si>
-  <si>
-    <t>G009.JPG</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -121,47 +42,85 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -449,134 +408,216 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="25.6640625" customWidth="1"/>
-    <col min="3" max="3" width="11.88671875" customWidth="1"/>
-    <col min="5" max="5" width="15" style="2" customWidth="1"/>
-    <col min="6" max="6" width="13.77734375" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>13</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>mrp</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>rate</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>image_name</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>H001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>LOTUS DOOR HANDLE</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
         <v>80000</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>50000</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" t="s">
-        <v>2</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>H001.JPG</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3">
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>H002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SHINE DOOR HANDLE </t>
+        </is>
+      </c>
+      <c r="C3" t="n">
         <v>8000</v>
       </c>
-      <c r="D3">
+      <c r="D3" t="n">
         <v>2800</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" t="s">
-        <v>2</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>H002.JPG</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>M010</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUSHPA DOOR HANDLE </t>
+        </is>
+      </c>
+      <c r="C4" t="n">
         <v>6000</v>
       </c>
-      <c r="D4">
+      <c r="D4" t="n">
         <v>5500</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" t="s">
-        <v>2</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>M010.JPG</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5">
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>P005</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JAYA DOOR HANDLE </t>
+        </is>
+      </c>
+      <c r="C5" t="n">
         <v>3000</v>
       </c>
-      <c r="D5">
+      <c r="D5" t="n">
         <v>450</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" t="s">
-        <v>2</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>P005.JPG</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6">
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>G009</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Crystal Glass Handle</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
         <v>4000</v>
       </c>
-      <c r="D6">
+      <c r="D6" t="n">
         <v>3200</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" t="s">
-        <v>2</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>G009.JPG</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PULL HANDLE 001</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JAYA HANDLE </t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>25000</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>ChatGPT Image Feb 13, 2026, 04_30_19 PM.png</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -599,22 +599,106 @@
           <t xml:space="preserve">JAYA HANDLE </t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D7" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>ChatGPT Image Feb 13, 2026, 04_30_19 PM.png</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PULL HANDLE 001</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JAYA HANDLE </t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D8" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>ChatGPT Image Feb 13, 2026, 04_30_19 PM.png</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PULL HANDLE 001</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JAYA HANDLE </t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D9" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>ChatGPT Image Feb 13, 2026, 04_30_19 PM.png</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PULL HANDLE 001</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JAYA HANDLE </t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
         <is>
           <t>30000</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>25000</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>ChatGPT Image Feb 13, 2026, 04_30_19 PM.png</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Available</t>
         </is>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,15 +683,11 @@
           <t xml:space="preserve">JAYA HANDLE </t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>30000</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>25000</t>
-        </is>
+      <c r="C10" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D10" t="n">
+        <v>25000</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -699,6 +695,38 @@
         </is>
       </c>
       <c r="F10" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>DOOR HANDLE</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KISHORE </t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>9999</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Gemini_Generated_Image_vhr0y2vhr0y2vhr0.png</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>Available</t>
         </is>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -711,22 +711,106 @@
           <t xml:space="preserve">KISHORE </t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D11" t="n">
+        <v>9999</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Gemini_Generated_Image_vhr0y2vhr0y2vhr0.png</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>DOOR HANDLE</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KISHORE </t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D12" t="n">
+        <v>9999</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Gemini_Generated_Image_vhr0y2vhr0y2vhr0.png</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>DOOR HANDLE</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KISHORE </t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D13" t="n">
+        <v>9999</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Gemini_Generated_Image_vhr0y2vhr0y2vhr0.png</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>DOOR HANDLE</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KISHORE </t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>9999</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Gemini_Generated_Image_vhr0y2vhr0y2vhr0.png</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Available</t>
         </is>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -795,15 +795,11 @@
           <t xml:space="preserve">KISHORE </t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>10000</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>9999</t>
-        </is>
+      <c r="C14" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D14" t="n">
+        <v>9999</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -811,6 +807,38 @@
         </is>
       </c>
       <c r="F14" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MANDLA </t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>LOTUSSS</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>300000</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>ChatGPT Image Feb 15, 2026, 01_07_28 PM.png</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>Available</t>
         </is>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,47 +484,100 @@
           <t xml:space="preserve">JAYA HANDLE </t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>30000</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+      <c r="C2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>BRASS</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>24"</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>ANTQ</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Per Set</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>HII</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>ChatGPT Image Feb 8, 2026, 10_25_51 PM.png</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>DOOR HANDLE</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>LOTUSSS</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>25000</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>BRASS</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>24"</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>34"</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>ANTQ</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Per Set</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>HII</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>ChatGPT Image Feb 8, 2026, 10_25_51 PM.png</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Gemini_Generated_Image_524m5r524m5r524m.png</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>Available</t>
         </is>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -537,47 +537,100 @@
           <t>LOTUSSS</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D3" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>BRASS</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>34"</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ANTQ</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Per Set</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Gemini_Generated_Image_524m5r524m5r524m.png</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MANDLA </t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KISHORE </t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>25000</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>BRASS</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>34"</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>ANTQ</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>9999</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>S.S.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>249"</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>BLACK</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t>Per Set</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>GOOD</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Gemini_Generated_Image_524m5r524m5r524m.png</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THIS IS TO GOOD TO HANDLE AND ALSO </t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ChatGPT Image Feb 15, 2026, 01_32_57 PM.png,ChatGPT Image Feb 15, 2026, 01_31_37 PM.png,ChatGPT Image Feb 15, 2026, 01_28_47 PM.png,Gemini_Generated_Image_1sb8oe1sb8oe1sb8.png,Gemini_Generated_Image_iu3mkpiu3mkpiu3m.png</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>Available</t>
         </is>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,6 +472,11 @@
           <t>status</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -525,6 +530,7 @@
           <t>Available</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -578,6 +584,7 @@
           <t>Available</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -590,49 +597,108 @@
           <t xml:space="preserve">KISHORE </t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D4" t="n">
+        <v>9999</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>S.S.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>249"</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>BLACK</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Per Set</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THIS IS TO GOOD TO HANDLE AND ALSO </t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ChatGPT Image Feb 15, 2026, 01_32_57 PM.png,ChatGPT Image Feb 15, 2026, 01_31_37 PM.png,ChatGPT Image Feb 15, 2026, 01_28_47 PM.png,Gemini_Generated_Image_1sb8oe1sb8oe1sb8.png,Gemini_Generated_Image_iu3mkpiu3mkpiu3m.png</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>PULL HANDLE 001</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>9999</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>S.S.</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>249"</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>BLACK</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Per Set</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">THIS IS TO GOOD TO HANDLE AND ALSO </t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>ChatGPT Image Feb 15, 2026, 01_32_57 PM.png,ChatGPT Image Feb 15, 2026, 01_31_37 PM.png,ChatGPT Image Feb 15, 2026, 01_28_47 PM.png,Gemini_Generated_Image_1sb8oe1sb8oe1sb8.png,Gemini_Generated_Image_iu3mkpiu3mkpiu3m.png</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>BRASS</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>12"</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ANTQ</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Per Pcs</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>QWQQWQWQWQWQWQ</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ChatGPT Image Feb 15, 2026, 01_28_47 PM.png,ChatGPT Image Feb 15, 2026, 01_32_57 PM.png,ChatGPT Image Feb 15, 2026, 01_31_37 PM.png</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>Available</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Cabinet Handle</t>
         </is>
       </c>
     </row>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,14 +486,14 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">JAYA HANDLE </t>
+          <t>D</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>30000</v>
+        <v>10000</v>
       </c>
       <c r="D2" t="n">
-        <v>25000</v>
+        <v>9999</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -502,7 +502,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>24"</t>
+          <t>12"</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -512,17 +512,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Per Set</t>
+          <t>Per Pcs</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>HII</t>
+          <t>QWQQWQWQWQWQWQ</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>ChatGPT Image Feb 8, 2026, 10_25_51 PM.png</t>
+          <t>ChatGPT Image Feb 15, 2026, 01_28_47 PM.png,ChatGPT Image Feb 15, 2026, 01_32_57 PM.png,ChatGPT Image Feb 15, 2026, 01_31_37 PM.png</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -530,173 +530,7 @@
           <t>Available</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>DOOR HANDLE</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>LOTUSSS</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>10000</v>
-      </c>
-      <c r="D3" t="n">
-        <v>25000</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>BRASS</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>34"</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>ANTQ</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Per Set</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>GOOD</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Gemini_Generated_Image_524m5r524m5r524m.png</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MANDLA </t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">KISHORE </t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10000</v>
-      </c>
-      <c r="D4" t="n">
-        <v>9999</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>S.S.</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>249"</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>BLACK</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Per Set</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">THIS IS TO GOOD TO HANDLE AND ALSO </t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>ChatGPT Image Feb 15, 2026, 01_32_57 PM.png,ChatGPT Image Feb 15, 2026, 01_31_37 PM.png,ChatGPT Image Feb 15, 2026, 01_28_47 PM.png,Gemini_Generated_Image_1sb8oe1sb8oe1sb8.png,Gemini_Generated_Image_iu3mkpiu3mkpiu3m.png</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>PULL HANDLE 001</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>10000</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>9999</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>BRASS</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>12"</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>ANTQ</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Per Pcs</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>QWQQWQWQWQWQWQ</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>ChatGPT Image Feb 15, 2026, 01_28_47 PM.png,ChatGPT Image Feb 15, 2026, 01_32_57 PM.png,ChatGPT Image Feb 15, 2026, 01_31_37 PM.png</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Cabinet Handle</t>
         </is>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -533,6 +533,68 @@
       <c r="L2" t="inlineStr">
         <is>
           <t>Cabinet Handle</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>PULL HANDLE 001</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JAYA HANDLE </t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>300000</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>BRASS</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>12"</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ANTQ</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Per Pcs</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THIS IS A HARDWARE HANDLE </t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ChatGPT Image Feb 15, 2026, 01_32_57 PM.png,ChatGPT Image Feb 15, 2026, 01_31_37 PM.png,ChatGPT Image Feb 15, 2026, 01_28_47 PM.png</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Accessories</t>
         </is>
       </c>
     </row>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -547,56 +547,82 @@
           <t xml:space="preserve">JAYA HANDLE </t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>300000</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+      <c r="C3" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D3" t="n">
+        <v>200000</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>BRASS</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>12"</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ANTQ</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Per Pcs</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THIS IS A HARDWARE HANDLE </t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ChatGPT Image Feb 15, 2026, 01_32_57 PM.png,ChatGPT Image Feb 15, 2026, 01_31_37 PM.png,ChatGPT Image Feb 15, 2026, 01_28_47 PM.png</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>PULL HANDLE 444</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JAYA HANDLE </t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
         <is>
           <t>200000</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>BRASS</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>12"</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>ANTQ</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Per Pcs</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">THIS IS A HARDWARE HANDLE </t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>ChatGPT Image Feb 15, 2026, 01_32_57 PM.png,ChatGPT Image Feb 15, 2026, 01_31_37 PM.png,ChatGPT Image Feb 15, 2026, 01_28_47 PM.png</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ChatGPT Image Feb 15, 2026, 01_28_47 PM.png</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -606,10 +606,8 @@
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>200000</t>
-        </is>
+      <c r="D4" t="n">
+        <v>200000</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
@@ -624,6 +622,36 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>DOOR HANDLE</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>FUNK</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>25000</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Gemini_Generated_Image_fu1ustfu1ustfu1u.png</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
